--- a/Construction/BOM_Aug_18_2026.xlsx
+++ b/Construction/BOM_Aug_18_2026.xlsx
@@ -3,19 +3,32 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD8A731-F043-425D-8FC6-CCDD8981336A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5D5BD2-4F21-4A96-A151-A4EBCB25908D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="222">
   <si>
     <t>Part Name</t>
   </si>
@@ -305,9 +318,6 @@
     <t>Servo Assembly (x4)</t>
   </si>
   <si>
-    <t>Side Supports (x4)</t>
-  </si>
-  <si>
     <t>Nylon Washer - M2.5</t>
   </si>
   <si>
@@ -594,24 +604,109 @@
   </si>
   <si>
     <t>Nut M2.5</t>
+  </si>
+  <si>
+    <t>Ultra Tiny USB Webcam Camera with GC0307 Sensor</t>
+  </si>
+  <si>
+    <t>Pinhole Camera</t>
+  </si>
+  <si>
+    <t>Side Supports (x4) - 1 Modified</t>
+  </si>
+  <si>
+    <t>SideSupportWire</t>
+  </si>
+  <si>
+    <t>Support to hold Servo Assemblies -&gt; 1x needed for wire passthrough</t>
+  </si>
+  <si>
+    <t>M2.5 Nut</t>
+  </si>
+  <si>
+    <t>Misc nuts</t>
+  </si>
+  <si>
+    <t>M2.5 Nylon Washer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Misc Washers  </t>
+  </si>
+  <si>
+    <t>M.25x8 Socket Head Screw</t>
+  </si>
+  <si>
+    <t>misc screws</t>
+  </si>
+  <si>
+    <t>INDIVIDUAL COUNTS</t>
+  </si>
+  <si>
+    <t>Aluminum</t>
+  </si>
+  <si>
+    <t>Binding Head Screw M3x5</t>
+  </si>
+  <si>
+    <t>JST1.5 3 Pin Connector</t>
+  </si>
+  <si>
+    <t>M3 Nut</t>
+  </si>
+  <si>
+    <t>M3 Nylon Washer</t>
+  </si>
+  <si>
+    <t>Horizontal bearing sleeves</t>
+  </si>
+  <si>
+    <t>Vertical Bearing Sleeves</t>
+  </si>
+  <si>
+    <t>Socket Head Screw M1.6x4</t>
+  </si>
+  <si>
+    <t>Socket Head Screw M2.5x4</t>
+  </si>
+  <si>
+    <t>Socket Head Screw M2.5x6</t>
+  </si>
+  <si>
+    <t>Socket Head Screw M2.5x8</t>
+  </si>
+  <si>
+    <t>Socket Head Screw M3x12</t>
+  </si>
+  <si>
+    <t>Socket Head Screw M3x20</t>
+  </si>
+  <si>
+    <t>Socket Head Screw M3x25</t>
+  </si>
+  <si>
+    <t>Socket Head Screw M3x30</t>
+  </si>
+  <si>
+    <t>Socket Head Screw M3x5</t>
+  </si>
+  <si>
+    <t>Tendons. Each approx 1.5ft.</t>
+  </si>
+  <si>
+    <t>TOTAL COUNTS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
@@ -638,16 +733,60 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -655,19 +794,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Calculation" xfId="2" builtinId="22"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1006,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
@@ -1014,14 +1173,19 @@
     <col min="3" max="3" width="87.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.28515625" style="1" customWidth="1"/>
     <col min="5" max="6" width="32" style="1" customWidth="1"/>
+    <col min="7" max="7" width="37" style="4" customWidth="1"/>
+    <col min="8" max="8" width="84.42578125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="25" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1029,18 +1193,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="G5" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>54</v>
       </c>
@@ -1056,17 +1229,41 @@
       <c r="E6" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G7" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D8" s="1">
@@ -1075,12 +1272,24 @@
       <c r="E8" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I8" s="7">
+        <v>1</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="1">
@@ -1089,12 +1298,24 @@
       <c r="E9" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G9" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I9" s="7">
+        <v>1</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D10" s="1">
@@ -1103,12 +1324,24 @@
       <c r="E10" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G10" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="7">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D11" s="1">
@@ -1117,12 +1350,24 @@
       <c r="E11" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I11" s="7">
+        <v>8</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D12" s="1">
@@ -1131,12 +1376,24 @@
       <c r="E12" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" s="7">
+        <v>12</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D13" s="1">
@@ -1145,12 +1402,24 @@
       <c r="E13" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="7">
+        <v>2</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D14" s="1">
@@ -1159,12 +1428,24 @@
       <c r="E14" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I14" s="7">
+        <v>8</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D15" s="1">
@@ -1173,12 +1454,24 @@
       <c r="E15" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I15" s="7">
+        <v>3</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D16" s="1">
@@ -1187,12 +1480,24 @@
       <c r="E16" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" s="7">
+        <v>3</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D17" s="1">
@@ -1201,12 +1506,24 @@
       <c r="E17" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G17" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I17" s="7">
+        <v>2</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D18" s="1">
@@ -1215,12 +1532,24 @@
       <c r="E18" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I18" s="7">
+        <v>16</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D19" s="1">
@@ -1229,68 +1558,128 @@
       <c r="E19" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+      <c r="G19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="7">
+        <v>6</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="D20" s="1">
         <v>5</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="3" t="s">
+      <c r="E20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" s="7">
+        <v>1</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="7">
+        <v>1</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I22" s="7">
+        <v>1</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="3" t="s">
+      <c r="E23" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I23" s="7">
+        <v>1</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D24" s="1">
@@ -1299,20 +1688,44 @@
       <c r="E24" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I24" s="7">
+        <v>1</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I25" s="7">
+        <v>1</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D26" s="1">
@@ -1321,12 +1734,24 @@
       <c r="E26" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G26" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I26" s="7">
+        <v>1</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D27" s="1">
@@ -1335,12 +1760,24 @@
       <c r="E27" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G27" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="I27" s="7">
+        <v>1</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D28" s="1">
@@ -1349,12 +1786,24 @@
       <c r="E28" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="I28" s="7">
+        <v>1</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D29" s="1">
@@ -1363,12 +1812,24 @@
       <c r="E29" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I29" s="7">
+        <v>1</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D30" s="1">
@@ -1377,12 +1838,24 @@
       <c r="E30" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G30" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I30" s="7">
+        <v>24</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D31" s="1">
@@ -1391,12 +1864,24 @@
       <c r="E31" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G31" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="I31" s="7">
+        <v>2</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D32" s="1">
@@ -1405,12 +1890,24 @@
       <c r="E32" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="G32" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I32" s="7">
+        <v>1</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="2" t="s">
         <v>81</v>
       </c>
       <c r="D33" s="1">
@@ -1419,12 +1916,24 @@
       <c r="E33" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I33" s="7">
+        <v>1</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D34" s="1">
@@ -1433,12 +1942,24 @@
       <c r="E34" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
+      <c r="G34" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="I34" s="7">
+        <v>1</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D35" s="1">
@@ -1447,122 +1968,244 @@
       <c r="E35" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G35" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I35" s="7">
+        <v>5</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="C36" s="2"/>
+      <c r="G36" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I36" s="7">
+        <v>1</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="3" t="s">
+      <c r="C37" s="2"/>
+      <c r="G37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I37" s="7">
+        <v>1</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="3">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3" t="s">
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="G38" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I38" s="7">
+        <v>5</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D39" s="1">
         <v>4</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B40" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>100</v>
+      <c r="G39" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I39" s="7">
+        <v>2</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="D40" s="1">
         <v>4</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B41" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>101</v>
+      <c r="G40" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="I40" s="7">
+        <v>1</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D41" s="1">
         <v>4</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I41" s="7">
+        <v>3</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>102</v>
+      <c r="C42" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="D42" s="1">
         <v>1</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G42" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I42" s="7">
+        <v>1</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>103</v>
+      <c r="C43" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="D43" s="1">
         <v>2</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G43" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I43" s="7">
+        <v>1</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>104</v>
+      <c r="C44" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G44" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I44" s="7">
+        <v>1</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>105</v>
+      <c r="C45" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="D45" s="1">
         <v>1</v>
@@ -1570,13 +2213,25 @@
       <c r="E45" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G45" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I45" s="7">
+        <v>1</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>106</v>
+      <c r="C46" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="D46" s="1">
         <v>1</v>
@@ -1584,724 +2239,1295 @@
       <c r="E46" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G46" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I46" s="7">
+        <v>21</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I47" s="7">
+        <v>39</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="1">
-        <v>1</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="D48" s="1">
         <v>4</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="3" t="s">
+      <c r="E48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="H48" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>111</v>
+      <c r="I48" s="7">
+        <v>11</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="D49" s="1">
         <v>4</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I49" s="7">
+        <v>22</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50" s="1">
+        <v>1</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I50" s="7">
+        <v>1</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D50" s="1">
-        <v>1</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D51" s="1">
         <v>3</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="3" t="s">
+      <c r="E51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I51" s="7">
+        <v>1</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B52" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I52" s="7">
+        <v>3</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B53" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D52" s="1">
-        <v>1</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="D53" s="1">
         <v>2</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="3" t="s">
+      <c r="E53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I53" s="7">
+        <v>1</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B54" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="D54" s="1">
         <v>1</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I54" s="7">
+        <v>1</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="G55" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="I55" s="7">
+        <v>3</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>121</v>
+      <c r="C56" s="2" t="s">
+        <v>120</v>
       </c>
       <c r="D56" s="1">
         <v>3</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G56" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I56" s="7">
+        <v>1</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="I57" s="7">
+        <v>1</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="2"/>
+      <c r="B58" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I58" s="7">
+        <v>1</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D59" s="2">
+        <v>1</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I59" s="7">
+        <v>1</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B60" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D57" s="1">
-        <v>1</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="4"/>
-      <c r="B58" s="3" t="s">
+      <c r="C60" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I60" s="7">
+        <v>10</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="I61" s="7">
+        <v>2</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I62" s="7">
+        <v>1</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="I63" s="7">
+        <v>8</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" s="1">
+        <v>12</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I64" s="7">
+        <v>1</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" s="1">
+        <v>8</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I65" s="7">
+        <v>1</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D66" s="1">
+        <v>24</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="I66" s="7">
+        <v>1</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D67" s="1">
+        <v>16</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I67" s="7">
+        <v>1</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B68" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="1">
+        <v>3</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="I68" s="7">
+        <v>1</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B69" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H69" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D58" s="1">
-        <v>1</v>
-      </c>
-      <c r="E58" s="3" t="s">
+      <c r="I69" s="7">
+        <v>1</v>
+      </c>
+      <c r="J69" s="7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="3" t="s">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B70" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D70" s="1">
+        <v>8</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="I70" s="7">
+        <v>16</v>
+      </c>
+      <c r="J70" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B71" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D71" s="1">
+        <v>3</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I71" s="7">
+        <v>2</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D72" s="1">
+        <v>1</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="H72" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="I72" s="7">
+        <v>1</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B73" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D73" s="1">
+        <v>8</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I73" s="7">
+        <v>3</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B74" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D74" s="1">
+        <v>4</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D59" s="1">
-        <v>1</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C60" s="1" t="s">
+      <c r="G74" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I74" s="7">
+        <v>19</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B75" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D75" s="1">
+        <v>14</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I75" s="7">
+        <v>4</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B76" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D76" s="1">
+        <v>7</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I76" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B61" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C61" s="3" t="s">
+      <c r="J76" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B77" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D77" s="1">
+        <v>1</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I77" s="7">
+        <v>4</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B78" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D78" s="1">
+        <v>3</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I78" s="7">
+        <v>4</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I79" s="7">
+        <v>1</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B80" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D80" s="1">
+        <v>1</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I80" s="7">
+        <v>1</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B81" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D81" s="1">
+        <v>1</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="I81" s="7">
+        <v>1</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B82" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="I82" s="7">
+        <v>8</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B83" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D83" s="1">
+        <v>1</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I83" s="7">
+        <v>4</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B84" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D84" s="1">
+        <v>1</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="I84" s="7">
+        <v>4</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B85" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D85" s="1">
+        <v>1</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="I85" s="7">
+        <v>1</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B86" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D86" s="1">
+        <v>1</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H86" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D61" s="1">
-        <v>1</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D62" s="1">
-        <v>1</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B63" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D63" s="1">
-        <v>11</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B64" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D64" s="1">
-        <v>8</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B65" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D65" s="1">
-        <v>24</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B66" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D66" s="1">
-        <v>16</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B67" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D67" s="1">
-        <v>3</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B68" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D68" s="1">
-        <v>1</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B69" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D69" s="1">
-        <v>8</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B70" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D70" s="1">
-        <v>3</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B71" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D71" s="1">
-        <v>1</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B72" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D72" s="1">
-        <v>8</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B73" s="3" t="s">
+      <c r="I86" s="7">
+        <v>1</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B87" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D87" s="1">
+        <v>1</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I87" s="7">
+        <v>5</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B88" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D88" s="1">
+        <v>1</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B89" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D89" s="1">
+        <v>4</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B90" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D90" s="1">
+        <v>1</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B91" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D91" s="1">
+        <v>13</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B92" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D92" s="1">
+        <v>13</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B93" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D93" s="1">
+        <v>7</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C94" s="2"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B95" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D95" s="1">
+        <v>22</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B96" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D96" s="1">
+        <v>12</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B97" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D97" s="1">
+        <v>1</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B98" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C98" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D98" s="1">
+        <v>4</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B99" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D99" s="1">
+        <v>2</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B100" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D100" s="1">
+        <v>1</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B101" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D101" s="1">
+        <v>1</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B102" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D102" s="1">
+        <v>4</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B103" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D73" s="1">
-        <v>4</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B74" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D74" s="1">
-        <v>14</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B75" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D75" s="1">
+      <c r="D103" s="1">
         <v>7</v>
       </c>
-      <c r="E75" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B76" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D76" s="1">
-        <v>3</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B78" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D78" s="1">
-        <v>1</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B79" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C79" s="3" t="s">
+      <c r="E103" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B104" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D104" s="1">
+        <v>1</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="D79" s="1">
-        <v>1</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B80" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D80" s="1">
-        <v>1</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B81" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D81" s="1">
-        <v>1</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B82" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D82" s="1">
-        <v>1</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B83" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D83" s="1">
-        <v>1</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B84" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D84" s="1">
-        <v>1</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B85" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D85" s="1">
-        <v>1</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B86" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D86" s="1">
-        <v>1</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B87" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D87" s="1">
-        <v>4</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B88" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D88" s="1">
-        <v>1</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B90" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D90" s="1">
-        <v>22</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B91" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="D91" s="1">
-        <v>12</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B92" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D92" s="1">
-        <v>1</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B93" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D93" s="1">
-        <v>4</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B94" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D94" s="1">
-        <v>2</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B95" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D95" s="1">
-        <v>1</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B96" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D96" s="1">
-        <v>1</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B97" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D97" s="1">
-        <v>4</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B98" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D98" s="1">
-        <v>7</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C125" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="127" spans="3:3" x14ac:dyDescent="0.25">
@@ -2324,11 +3550,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
     <row r="132" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -2384,8 +3605,33 @@
         <v>3</v>
       </c>
     </row>
+    <row r="143" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C143" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C145" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="146" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{CBBA7E6A-02A1-4B9F-9C4D-467260C066D9}"/>
   </hyperlinks>
